--- a/skills/mom-business-data-generator/templates/工厂资源_模板.xlsx
+++ b/skills/mom-business-data-generator/templates/工厂资源_模板.xlsx
@@ -20,12 +20,13 @@
     <sheet name="库房" r:id="rId14" sheetId="12"/>
     <sheet name="库位" r:id="rId15" sheetId="13"/>
     <sheet name="工序库" r:id="rId16" sheetId="14"/>
+    <sheet name="工序库与资质等级" r:id="rId17" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9294" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10708" uniqueCount="64">
   <si>
     <t>填写说明</t>
   </si>
@@ -56,6 +57,15 @@
   </si>
   <si>
     <t>启用</t>
+  </si>
+  <si>
+    <t>集成系统</t>
+  </si>
+  <si>
+    <t>集成数据主键</t>
+  </si>
+  <si>
+    <t>集成创建时间</t>
   </si>
   <si>
     <t>型号规格</t>
@@ -133,12 +143,6 @@
     <t>物料阶段</t>
   </si>
   <si>
-    <t>发布版本时间</t>
-  </si>
-  <si>
-    <t>发布人</t>
-  </si>
-  <si>
     <t>*版本号</t>
   </si>
   <si>
@@ -175,16 +179,22 @@
     <t>呆滞物料预警时长(年)</t>
   </si>
   <si>
-    <t>作业模式</t>
+    <t>*作业模式</t>
   </si>
   <si>
     <t>*业务类型</t>
   </si>
   <si>
+    <t>库区编码</t>
+  </si>
+  <si>
     <t>*库房编码</t>
   </si>
   <si>
-    <t>序专业类型</t>
+    <t>工序专业类型</t>
+  </si>
+  <si>
+    <t>组织</t>
   </si>
   <si>
     <t>*工序类型</t>
@@ -207,13 +217,19 @@
   <si>
     <t>工序内容</t>
   </si>
+  <si>
+    <t>*工序库编码</t>
+  </si>
+  <si>
+    <t>资质等级编码</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -230,6 +246,18 @@
     <font>
       <name val="Calibri"/>
       <sz val="12.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -446,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -571,6 +599,15 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -609,10 +646,10 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="28">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s" s="28">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -1431,10 +1468,10 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s" s="31">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -2251,7 +2288,7 @@
     <col min="2" max="2" width="17.0" customWidth="true"/>
     <col min="3" max="3" width="17.0" customWidth="true"/>
     <col min="4" max="4" width="9.0" customWidth="true"/>
-    <col min="5" max="5" width="10.0" customWidth="true"/>
+    <col min="5" max="5" width="11.0" customWidth="true"/>
     <col min="6" max="6" width="11.0" customWidth="true"/>
     <col min="7" max="7" width="9.0" customWidth="true"/>
     <col min="8" max="8" width="8.0" customWidth="true"/>
@@ -2260,22 +2297,22 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="34">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="33">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s" s="33">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s" s="33">
         <v>5</v>
       </c>
       <c r="E1" t="s" s="33">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s" s="33">
         <v>4</v>
@@ -5205,34 +5242,38 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.0" customWidth="true"/>
-    <col min="2" max="2" width="11.0" customWidth="true"/>
-    <col min="3" max="3" width="9.0" customWidth="true"/>
+    <col min="2" max="2" width="10.0" customWidth="true"/>
+    <col min="3" max="3" width="11.0" customWidth="true"/>
     <col min="4" max="4" width="9.0" customWidth="true"/>
-    <col min="5" max="5" width="8.0" customWidth="true"/>
-    <col min="6" max="6" width="9.0" customWidth="true"/>
+    <col min="5" max="5" width="9.0" customWidth="true"/>
+    <col min="6" max="6" width="8.0" customWidth="true"/>
+    <col min="7" max="7" width="9.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="37">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="37">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s" s="36">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s" s="37">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s" s="36">
         <v>5</v>
       </c>
-      <c r="D1" t="s" s="36">
+      <c r="E1" t="s" s="36">
         <v>4</v>
       </c>
-      <c r="E1" t="s" s="36">
+      <c r="F1" t="s" s="36">
         <v>6</v>
       </c>
-      <c r="F1" t="s" s="36">
+      <c r="G1" t="s" s="36">
         <v>2</v>
       </c>
     </row>
@@ -5255,6 +5296,9 @@
       <c r="F2" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G2" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="38" t="s">
@@ -5275,6 +5319,9 @@
       <c r="F3" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G3" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="38" t="s">
@@ -5295,6 +5342,9 @@
       <c r="F4" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="38" t="s">
@@ -5315,6 +5365,9 @@
       <c r="F5" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G5" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="38" t="s">
@@ -5335,6 +5388,9 @@
       <c r="F6" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G6" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="38" t="s">
@@ -5355,6 +5411,9 @@
       <c r="F7" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G7" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="38" t="s">
@@ -5375,6 +5434,9 @@
       <c r="F8" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G8" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="38" t="s">
@@ -5395,6 +5457,9 @@
       <c r="F9" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G9" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
@@ -5415,6 +5480,9 @@
       <c r="F10" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G10" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
@@ -5435,6 +5503,9 @@
       <c r="F11" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G11" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
@@ -5455,6 +5526,9 @@
       <c r="F12" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G12" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="38" t="s">
@@ -5475,6 +5549,9 @@
       <c r="F13" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G13" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="38" t="s">
@@ -5495,6 +5572,9 @@
       <c r="F14" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G14" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="38" t="s">
@@ -5515,6 +5595,9 @@
       <c r="F15" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G15" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="38" t="s">
@@ -5535,6 +5618,9 @@
       <c r="F16" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G16" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="38" t="s">
@@ -5555,6 +5641,9 @@
       <c r="F17" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G17" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="38" t="s">
@@ -5575,6 +5664,9 @@
       <c r="F18" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G18" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="38" t="s">
@@ -5595,6 +5687,9 @@
       <c r="F19" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G19" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="38" t="s">
@@ -5615,6 +5710,9 @@
       <c r="F20" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G20" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="38" t="s">
@@ -5635,6 +5733,9 @@
       <c r="F21" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G21" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="38" t="s">
@@ -5655,6 +5756,9 @@
       <c r="F22" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G22" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="38" t="s">
@@ -5675,6 +5779,9 @@
       <c r="F23" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G23" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="38" t="s">
@@ -5695,6 +5802,9 @@
       <c r="F24" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G24" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="38" t="s">
@@ -5715,6 +5825,9 @@
       <c r="F25" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G25" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="38" t="s">
@@ -5735,6 +5848,9 @@
       <c r="F26" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G26" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="38" t="s">
@@ -5755,6 +5871,9 @@
       <c r="F27" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G27" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="s">
@@ -5775,6 +5894,9 @@
       <c r="F28" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G28" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="s">
@@ -5795,6 +5917,9 @@
       <c r="F29" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G29" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="s">
@@ -5815,6 +5940,9 @@
       <c r="F30" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G30" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="38" t="s">
@@ -5835,6 +5963,9 @@
       <c r="F31" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G31" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="38" t="s">
@@ -5855,6 +5986,9 @@
       <c r="F32" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G32" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="38" t="s">
@@ -5875,6 +6009,9 @@
       <c r="F33" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G33" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="38" t="s">
@@ -5895,6 +6032,9 @@
       <c r="F34" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G34" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="38" t="s">
@@ -5915,6 +6055,9 @@
       <c r="F35" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G35" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="38" t="s">
@@ -5935,6 +6078,9 @@
       <c r="F36" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G36" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="38" t="s">
@@ -5955,6 +6101,9 @@
       <c r="F37" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G37" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="38" t="s">
@@ -5975,6 +6124,9 @@
       <c r="F38" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G38" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="38" t="s">
@@ -5995,6 +6147,9 @@
       <c r="F39" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G39" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="38" t="s">
@@ -6015,6 +6170,9 @@
       <c r="F40" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G40" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="s">
@@ -6035,6 +6193,9 @@
       <c r="F41" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G41" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="s">
@@ -6055,6 +6216,9 @@
       <c r="F42" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G42" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="38" t="s">
@@ -6075,6 +6239,9 @@
       <c r="F43" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G43" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="38" t="s">
@@ -6095,6 +6262,9 @@
       <c r="F44" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G44" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="38" t="s">
@@ -6115,6 +6285,9 @@
       <c r="F45" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G45" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="38" t="s">
@@ -6135,6 +6308,9 @@
       <c r="F46" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G46" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="38" t="s">
@@ -6155,6 +6331,9 @@
       <c r="F47" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G47" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="38" t="s">
@@ -6175,6 +6354,9 @@
       <c r="F48" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G48" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="38" t="s">
@@ -6195,6 +6377,9 @@
       <c r="F49" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G49" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="38" t="s">
@@ -6215,6 +6400,9 @@
       <c r="F50" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G50" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="38" t="s">
@@ -6235,6 +6423,9 @@
       <c r="F51" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G51" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="38" t="s">
@@ -6255,6 +6446,9 @@
       <c r="F52" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G52" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="38" t="s">
@@ -6275,6 +6469,9 @@
       <c r="F53" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G53" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="38" t="s">
@@ -6295,6 +6492,9 @@
       <c r="F54" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G54" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="38" t="s">
@@ -6315,6 +6515,9 @@
       <c r="F55" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G55" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="38" t="s">
@@ -6335,6 +6538,9 @@
       <c r="F56" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G56" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="38" t="s">
@@ -6355,6 +6561,9 @@
       <c r="F57" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G57" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="38" t="s">
@@ -6375,6 +6584,9 @@
       <c r="F58" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G58" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="38" t="s">
@@ -6395,6 +6607,9 @@
       <c r="F59" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G59" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="38" t="s">
@@ -6415,6 +6630,9 @@
       <c r="F60" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G60" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="38" t="s">
@@ -6435,6 +6653,9 @@
       <c r="F61" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G61" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="38" t="s">
@@ -6455,6 +6676,9 @@
       <c r="F62" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G62" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="38" t="s">
@@ -6475,6 +6699,9 @@
       <c r="F63" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G63" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="38" t="s">
@@ -6495,6 +6722,9 @@
       <c r="F64" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G64" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="38" t="s">
@@ -6515,6 +6745,9 @@
       <c r="F65" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G65" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="38" t="s">
@@ -6535,6 +6768,9 @@
       <c r="F66" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G66" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="38" t="s">
@@ -6555,6 +6791,9 @@
       <c r="F67" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G67" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="38" t="s">
@@ -6575,6 +6814,9 @@
       <c r="F68" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G68" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="38" t="s">
@@ -6595,6 +6837,9 @@
       <c r="F69" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G69" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="38" t="s">
@@ -6615,6 +6860,9 @@
       <c r="F70" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G70" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="38" t="s">
@@ -6635,6 +6883,9 @@
       <c r="F71" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G71" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="38" t="s">
@@ -6655,6 +6906,9 @@
       <c r="F72" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G72" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="38" t="s">
@@ -6675,6 +6929,9 @@
       <c r="F73" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G73" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="38" t="s">
@@ -6695,6 +6952,9 @@
       <c r="F74" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G74" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="38" t="s">
@@ -6715,6 +6975,9 @@
       <c r="F75" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G75" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="38" t="s">
@@ -6735,6 +6998,9 @@
       <c r="F76" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G76" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="38" t="s">
@@ -6755,6 +7021,9 @@
       <c r="F77" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G77" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="38" t="s">
@@ -6775,6 +7044,9 @@
       <c r="F78" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G78" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="38" t="s">
@@ -6795,6 +7067,9 @@
       <c r="F79" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G79" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="38" t="s">
@@ -6815,6 +7090,9 @@
       <c r="F80" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G80" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="38" t="s">
@@ -6835,6 +7113,9 @@
       <c r="F81" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G81" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="38" t="s">
@@ -6855,6 +7136,9 @@
       <c r="F82" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G82" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="38" t="s">
@@ -6875,6 +7159,9 @@
       <c r="F83" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G83" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="38" t="s">
@@ -6895,6 +7182,9 @@
       <c r="F84" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G84" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="38" t="s">
@@ -6915,6 +7205,9 @@
       <c r="F85" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G85" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="38" t="s">
@@ -6935,6 +7228,9 @@
       <c r="F86" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G86" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="38" t="s">
@@ -6955,6 +7251,9 @@
       <c r="F87" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G87" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="38" t="s">
@@ -6975,6 +7274,9 @@
       <c r="F88" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G88" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="38" t="s">
@@ -6995,6 +7297,9 @@
       <c r="F89" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G89" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="38" t="s">
@@ -7015,6 +7320,9 @@
       <c r="F90" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G90" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="38" t="s">
@@ -7035,6 +7343,9 @@
       <c r="F91" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G91" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="38" t="s">
@@ -7055,6 +7366,9 @@
       <c r="F92" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G92" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="38" t="s">
@@ -7075,6 +7389,9 @@
       <c r="F93" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G93" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="38" t="s">
@@ -7095,6 +7412,9 @@
       <c r="F94" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G94" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="38" t="s">
@@ -7115,6 +7435,9 @@
       <c r="F95" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G95" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="38" t="s">
@@ -7135,6 +7458,9 @@
       <c r="F96" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G96" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="38" t="s">
@@ -7155,6 +7481,9 @@
       <c r="F97" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G97" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="38" t="s">
@@ -7175,6 +7504,9 @@
       <c r="F98" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G98" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="38" t="s">
@@ -7195,6 +7527,9 @@
       <c r="F99" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G99" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="38" t="s">
@@ -7215,6 +7550,9 @@
       <c r="F100" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G100" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="38" t="s">
@@ -7235,10 +7573,13 @@
       <c r="F101" s="38" t="s">
         <v>3</v>
       </c>
+      <c r="G101" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="G2:G101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7248,21 +7589,22 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="11.0" customWidth="true"/>
+    <col min="2" max="2" width="12.0" customWidth="true"/>
     <col min="3" max="3" width="9.0" customWidth="true"/>
-    <col min="4" max="4" width="11.0" customWidth="true"/>
-    <col min="5" max="5" width="13.0" customWidth="true"/>
+    <col min="4" max="4" width="8.0" customWidth="true"/>
+    <col min="5" max="5" width="11.0" customWidth="true"/>
     <col min="6" max="6" width="13.0" customWidth="true"/>
     <col min="7" max="7" width="13.0" customWidth="true"/>
-    <col min="8" max="8" width="10.0" customWidth="true"/>
-    <col min="9" max="9" width="11.0" customWidth="true"/>
-    <col min="10" max="10" width="9.0" customWidth="true"/>
-    <col min="11" max="11" width="10.0" customWidth="true"/>
-    <col min="12" max="12" width="9.0" customWidth="true"/>
+    <col min="8" max="8" width="13.0" customWidth="true"/>
+    <col min="9" max="9" width="10.0" customWidth="true"/>
+    <col min="10" max="10" width="11.0" customWidth="true"/>
+    <col min="11" max="11" width="9.0" customWidth="true"/>
+    <col min="12" max="12" width="10.0" customWidth="true"/>
+    <col min="13" max="13" width="9.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -7270,36 +7612,39 @@
         <v>6</v>
       </c>
       <c r="B1" t="s" s="39">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s" s="39">
         <v>5</v>
       </c>
-      <c r="D1" t="s" s="39">
-        <v>52</v>
-      </c>
-      <c r="E1" t="s" s="40">
-        <v>44</v>
-      </c>
-      <c r="F1" t="s" s="39">
-        <v>53</v>
+      <c r="D1" t="s" s="40">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s" s="39">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s" s="40">
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="39">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s" s="39">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s" s="39">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s" s="39">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s" s="39">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L1" t="s" s="39">
+        <v>61</v>
+      </c>
+      <c r="M1" t="s" s="39">
         <v>2</v>
       </c>
     </row>
@@ -7340,6 +7685,9 @@
       <c r="L2" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M2" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="41" t="s">
@@ -7378,6 +7726,9 @@
       <c r="L3" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M3" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="s">
@@ -7416,6 +7767,9 @@
       <c r="L4" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M4" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="s">
@@ -7454,6 +7808,9 @@
       <c r="L5" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M5" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="41" t="s">
@@ -7492,6 +7849,9 @@
       <c r="L6" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M6" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="41" t="s">
@@ -7530,6 +7890,9 @@
       <c r="L7" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M7" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="s">
@@ -7568,6 +7931,9 @@
       <c r="L8" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M8" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="s">
@@ -7606,6 +7972,9 @@
       <c r="L9" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M9" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="s">
@@ -7644,6 +8013,9 @@
       <c r="L10" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M10" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="s">
@@ -7682,6 +8054,9 @@
       <c r="L11" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M11" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="s">
@@ -7720,6 +8095,9 @@
       <c r="L12" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M12" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="s">
@@ -7758,6 +8136,9 @@
       <c r="L13" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M13" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="s">
@@ -7796,6 +8177,9 @@
       <c r="L14" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M14" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="s">
@@ -7834,6 +8218,9 @@
       <c r="L15" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M15" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="s">
@@ -7872,6 +8259,9 @@
       <c r="L16" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M16" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="s">
@@ -7910,6 +8300,9 @@
       <c r="L17" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M17" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="41" t="s">
@@ -7948,6 +8341,9 @@
       <c r="L18" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M18" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="s">
@@ -7986,6 +8382,9 @@
       <c r="L19" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M19" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="s">
@@ -8024,6 +8423,9 @@
       <c r="L20" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M20" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="s">
@@ -8062,6 +8464,9 @@
       <c r="L21" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M21" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="s">
@@ -8100,6 +8505,9 @@
       <c r="L22" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M22" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="s">
@@ -8138,6 +8546,9 @@
       <c r="L23" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M23" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="s">
@@ -8176,6 +8587,9 @@
       <c r="L24" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M24" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="s">
@@ -8214,6 +8628,9 @@
       <c r="L25" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M25" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="s">
@@ -8252,6 +8669,9 @@
       <c r="L26" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M26" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="s">
@@ -8290,6 +8710,9 @@
       <c r="L27" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M27" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="41" t="s">
@@ -8328,6 +8751,9 @@
       <c r="L28" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M28" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="s">
@@ -8366,6 +8792,9 @@
       <c r="L29" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M29" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="41" t="s">
@@ -8404,6 +8833,9 @@
       <c r="L30" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M30" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="s">
@@ -8442,6 +8874,9 @@
       <c r="L31" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M31" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="s">
@@ -8480,6 +8915,9 @@
       <c r="L32" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M32" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="41" t="s">
@@ -8518,6 +8956,9 @@
       <c r="L33" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M33" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="41" t="s">
@@ -8556,6 +8997,9 @@
       <c r="L34" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M34" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="s">
@@ -8594,6 +9038,9 @@
       <c r="L35" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M35" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="41" t="s">
@@ -8632,6 +9079,9 @@
       <c r="L36" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M36" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="41" t="s">
@@ -8670,6 +9120,9 @@
       <c r="L37" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M37" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="41" t="s">
@@ -8708,6 +9161,9 @@
       <c r="L38" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M38" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="41" t="s">
@@ -8746,6 +9202,9 @@
       <c r="L39" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M39" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="41" t="s">
@@ -8784,6 +9243,9 @@
       <c r="L40" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M40" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="41" t="s">
@@ -8822,6 +9284,9 @@
       <c r="L41" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M41" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="41" t="s">
@@ -8860,6 +9325,9 @@
       <c r="L42" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M42" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="41" t="s">
@@ -8898,6 +9366,9 @@
       <c r="L43" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M43" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="41" t="s">
@@ -8936,6 +9407,9 @@
       <c r="L44" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M44" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="41" t="s">
@@ -8974,6 +9448,9 @@
       <c r="L45" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M45" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="41" t="s">
@@ -9012,6 +9489,9 @@
       <c r="L46" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M46" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="41" t="s">
@@ -9050,6 +9530,9 @@
       <c r="L47" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M47" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="41" t="s">
@@ -9088,6 +9571,9 @@
       <c r="L48" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M48" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="41" t="s">
@@ -9126,6 +9612,9 @@
       <c r="L49" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M49" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="41" t="s">
@@ -9164,6 +9653,9 @@
       <c r="L50" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M50" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="41" t="s">
@@ -9202,6 +9694,9 @@
       <c r="L51" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M51" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="41" t="s">
@@ -9240,6 +9735,9 @@
       <c r="L52" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M52" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="41" t="s">
@@ -9278,6 +9776,9 @@
       <c r="L53" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M53" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="41" t="s">
@@ -9316,6 +9817,9 @@
       <c r="L54" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M54" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="41" t="s">
@@ -9354,6 +9858,9 @@
       <c r="L55" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M55" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="41" t="s">
@@ -9392,6 +9899,9 @@
       <c r="L56" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M56" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="41" t="s">
@@ -9430,6 +9940,9 @@
       <c r="L57" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M57" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="41" t="s">
@@ -9468,6 +9981,9 @@
       <c r="L58" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M58" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="41" t="s">
@@ -9506,6 +10022,9 @@
       <c r="L59" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M59" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="41" t="s">
@@ -9544,6 +10063,9 @@
       <c r="L60" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M60" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="41" t="s">
@@ -9582,6 +10104,9 @@
       <c r="L61" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M61" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="41" t="s">
@@ -9620,6 +10145,9 @@
       <c r="L62" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M62" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="41" t="s">
@@ -9658,6 +10186,9 @@
       <c r="L63" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M63" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="41" t="s">
@@ -9696,6 +10227,9 @@
       <c r="L64" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M64" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="41" t="s">
@@ -9734,6 +10268,9 @@
       <c r="L65" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M65" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="s">
@@ -9772,6 +10309,9 @@
       <c r="L66" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M66" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="41" t="s">
@@ -9810,6 +10350,9 @@
       <c r="L67" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M67" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="41" t="s">
@@ -9848,6 +10391,9 @@
       <c r="L68" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M68" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="41" t="s">
@@ -9886,6 +10432,9 @@
       <c r="L69" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M69" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="41" t="s">
@@ -9924,6 +10473,9 @@
       <c r="L70" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M70" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="41" t="s">
@@ -9962,6 +10514,9 @@
       <c r="L71" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M71" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="41" t="s">
@@ -10000,6 +10555,9 @@
       <c r="L72" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M72" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="41" t="s">
@@ -10038,6 +10596,9 @@
       <c r="L73" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M73" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="41" t="s">
@@ -10076,6 +10637,9 @@
       <c r="L74" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M74" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="s">
@@ -10114,6 +10678,9 @@
       <c r="L75" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M75" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="41" t="s">
@@ -10152,6 +10719,9 @@
       <c r="L76" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M76" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="41" t="s">
@@ -10190,6 +10760,9 @@
       <c r="L77" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M77" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="s">
@@ -10228,6 +10801,9 @@
       <c r="L78" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M78" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="41" t="s">
@@ -10266,6 +10842,9 @@
       <c r="L79" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M79" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="41" t="s">
@@ -10304,6 +10883,9 @@
       <c r="L80" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M80" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="41" t="s">
@@ -10342,6 +10924,9 @@
       <c r="L81" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M81" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="41" t="s">
@@ -10380,6 +10965,9 @@
       <c r="L82" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M82" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="41" t="s">
@@ -10418,6 +11006,9 @@
       <c r="L83" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M83" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="41" t="s">
@@ -10456,6 +11047,9 @@
       <c r="L84" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M84" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="41" t="s">
@@ -10494,6 +11088,9 @@
       <c r="L85" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M85" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="41" t="s">
@@ -10532,6 +11129,9 @@
       <c r="L86" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M86" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="41" t="s">
@@ -10570,6 +11170,9 @@
       <c r="L87" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M87" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="41" t="s">
@@ -10608,6 +11211,9 @@
       <c r="L88" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M88" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="41" t="s">
@@ -10646,6 +11252,9 @@
       <c r="L89" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M89" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="41" t="s">
@@ -10684,6 +11293,9 @@
       <c r="L90" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M90" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="41" t="s">
@@ -10722,6 +11334,9 @@
       <c r="L91" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M91" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="41" t="s">
@@ -10760,6 +11375,9 @@
       <c r="L92" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M92" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="41" t="s">
@@ -10798,6 +11416,9 @@
       <c r="L93" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M93" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="41" t="s">
@@ -10836,6 +11457,9 @@
       <c r="L94" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M94" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="41" t="s">
@@ -10874,6 +11498,9 @@
       <c r="L95" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M95" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="41" t="s">
@@ -10912,6 +11539,9 @@
       <c r="L96" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M96" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="41" t="s">
@@ -10950,6 +11580,9 @@
       <c r="L97" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M97" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="41" t="s">
@@ -10988,6 +11621,9 @@
       <c r="L98" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M98" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="41" t="s">
@@ -11026,6 +11662,9 @@
       <c r="L99" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M99" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="41" t="s">
@@ -11064,6 +11703,9 @@
       <c r="L100" s="41" t="s">
         <v>3</v>
       </c>
+      <c r="M100" s="41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="41" t="s">
@@ -11100,6 +11742,9 @@
         <v>3</v>
       </c>
       <c r="L101" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="41" t="s">
         <v>3</v>
       </c>
     </row>
@@ -11108,16 +11753,16 @@
     <dataValidation type="list" sqref="B2:B101" allowBlank="true" errorStyle="stop">
       <formula1>"机械加工专业,装配专业"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="E2:E101" allowBlank="true" errorStyle="stop">
       <formula1>"加工,检验,厂际转工,厂内转工,外委"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="I2:I101" allowBlank="true" errorStyle="stop">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="J2:J101" allowBlank="true" errorStyle="stop">
       <formula1>"天,小时,分钟,秒"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="M2:M101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11125,9 +11770,831 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.0" customWidth="true"/>
+    <col min="2" max="2" width="12.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.0" customHeight="true">
+      <c r="A1" t="s" s="43">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s" s="43">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.0" customWidth="true"/>
@@ -11136,6 +12603,9 @@
     <col min="4" max="4" width="8.0" customWidth="true"/>
     <col min="5" max="5" width="8.0" customWidth="true"/>
     <col min="6" max="6" width="8.0" customWidth="true"/>
+    <col min="7" max="7" width="10.0" customWidth="true"/>
+    <col min="8" max="8" width="12.0" customWidth="true"/>
+    <col min="9" max="9" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -11157,6 +12627,15 @@
       <c r="F1" t="s" s="3">
         <v>8</v>
       </c>
+      <c r="G1" t="s" s="3">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s" s="3">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
@@ -11177,6 +12656,15 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
@@ -11197,6 +12685,15 @@
       <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -11217,6 +12714,15 @@
       <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
@@ -11237,6 +12743,15 @@
       <c r="F5" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
@@ -11257,6 +12772,15 @@
       <c r="F6" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
@@ -11277,6 +12801,15 @@
       <c r="F7" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
@@ -11297,6 +12830,15 @@
       <c r="F8" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
@@ -11317,6 +12859,15 @@
       <c r="F9" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
@@ -11337,6 +12888,15 @@
       <c r="F10" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
@@ -11357,6 +12917,15 @@
       <c r="F11" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
@@ -11377,6 +12946,15 @@
       <c r="F12" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
@@ -11397,6 +12975,15 @@
       <c r="F13" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
@@ -11417,6 +13004,15 @@
       <c r="F14" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
@@ -11437,6 +13033,15 @@
       <c r="F15" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
@@ -11457,6 +13062,15 @@
       <c r="F16" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
@@ -11477,6 +13091,15 @@
       <c r="F17" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
@@ -11497,6 +13120,15 @@
       <c r="F18" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
@@ -11517,6 +13149,15 @@
       <c r="F19" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
@@ -11537,6 +13178,15 @@
       <c r="F20" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
@@ -11557,6 +13207,15 @@
       <c r="F21" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
@@ -11577,6 +13236,15 @@
       <c r="F22" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
@@ -11597,6 +13265,15 @@
       <c r="F23" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
@@ -11617,6 +13294,15 @@
       <c r="F24" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
@@ -11637,6 +13323,15 @@
       <c r="F25" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
@@ -11657,6 +13352,15 @@
       <c r="F26" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
@@ -11677,6 +13381,15 @@
       <c r="F27" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
@@ -11697,6 +13410,15 @@
       <c r="F28" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
@@ -11717,6 +13439,15 @@
       <c r="F29" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
@@ -11737,6 +13468,15 @@
       <c r="F30" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
@@ -11757,6 +13497,15 @@
       <c r="F31" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
@@ -11777,6 +13526,15 @@
       <c r="F32" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
@@ -11797,6 +13555,15 @@
       <c r="F33" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
@@ -11817,6 +13584,15 @@
       <c r="F34" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
@@ -11837,6 +13613,15 @@
       <c r="F35" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
@@ -11857,6 +13642,15 @@
       <c r="F36" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
@@ -11877,6 +13671,15 @@
       <c r="F37" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
@@ -11897,6 +13700,15 @@
       <c r="F38" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G38" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
@@ -11917,6 +13729,15 @@
       <c r="F39" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G39" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
@@ -11937,6 +13758,15 @@
       <c r="F40" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
@@ -11957,6 +13787,15 @@
       <c r="F41" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
@@ -11977,6 +13816,15 @@
       <c r="F42" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
@@ -11997,6 +13845,15 @@
       <c r="F43" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
@@ -12017,6 +13874,15 @@
       <c r="F44" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
@@ -12037,6 +13903,15 @@
       <c r="F45" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
@@ -12057,6 +13932,15 @@
       <c r="F46" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
@@ -12077,6 +13961,15 @@
       <c r="F47" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G47" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
@@ -12097,6 +13990,15 @@
       <c r="F48" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G48" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
@@ -12117,6 +14019,15 @@
       <c r="F49" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
@@ -12137,6 +14048,15 @@
       <c r="F50" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
@@ -12157,6 +14077,15 @@
       <c r="F51" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G51" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
@@ -12177,6 +14106,15 @@
       <c r="F52" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
@@ -12197,6 +14135,15 @@
       <c r="F53" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
@@ -12217,6 +14164,15 @@
       <c r="F54" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G54" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
@@ -12237,6 +14193,15 @@
       <c r="F55" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
@@ -12257,6 +14222,15 @@
       <c r="F56" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G56" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
@@ -12277,6 +14251,15 @@
       <c r="F57" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G57" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
@@ -12297,6 +14280,15 @@
       <c r="F58" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G58" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
@@ -12317,6 +14309,15 @@
       <c r="F59" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G59" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
@@ -12337,6 +14338,15 @@
       <c r="F60" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G60" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
@@ -12357,6 +14367,15 @@
       <c r="F61" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
@@ -12377,6 +14396,15 @@
       <c r="F62" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G62" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
@@ -12397,6 +14425,15 @@
       <c r="F63" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G63" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
@@ -12417,6 +14454,15 @@
       <c r="F64" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G64" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
@@ -12437,6 +14483,15 @@
       <c r="F65" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G65" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
@@ -12457,6 +14512,15 @@
       <c r="F66" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G66" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
@@ -12477,6 +14541,15 @@
       <c r="F67" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G67" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
@@ -12497,6 +14570,15 @@
       <c r="F68" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G68" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
@@ -12517,6 +14599,15 @@
       <c r="F69" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G69" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
@@ -12537,6 +14628,15 @@
       <c r="F70" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G70" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
@@ -12557,6 +14657,15 @@
       <c r="F71" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G71" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
@@ -12577,6 +14686,15 @@
       <c r="F72" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G72" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
@@ -12597,6 +14715,15 @@
       <c r="F73" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G73" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
@@ -12617,6 +14744,15 @@
       <c r="F74" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G74" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
@@ -12637,6 +14773,15 @@
       <c r="F75" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G75" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
@@ -12657,6 +14802,15 @@
       <c r="F76" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G76" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
@@ -12677,6 +14831,15 @@
       <c r="F77" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G77" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
@@ -12697,6 +14860,15 @@
       <c r="F78" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G78" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
@@ -12717,6 +14889,15 @@
       <c r="F79" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G79" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
@@ -12737,6 +14918,15 @@
       <c r="F80" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G80" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
@@ -12757,6 +14947,15 @@
       <c r="F81" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G81" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
@@ -12777,6 +14976,15 @@
       <c r="F82" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G82" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
@@ -12797,6 +15005,15 @@
       <c r="F83" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G83" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
@@ -12817,6 +15034,15 @@
       <c r="F84" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G84" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
@@ -12837,6 +15063,15 @@
       <c r="F85" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G85" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
@@ -12857,6 +15092,15 @@
       <c r="F86" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G86" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
@@ -12877,6 +15121,15 @@
       <c r="F87" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G87" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
@@ -12897,6 +15150,15 @@
       <c r="F88" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G88" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
@@ -12917,6 +15179,15 @@
       <c r="F89" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G89" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
@@ -12937,6 +15208,15 @@
       <c r="F90" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G90" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
@@ -12957,6 +15237,15 @@
       <c r="F91" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G91" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
@@ -12977,6 +15266,15 @@
       <c r="F92" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G92" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
@@ -12997,6 +15295,15 @@
       <c r="F93" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G93" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
@@ -13017,6 +15324,15 @@
       <c r="F94" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G94" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
@@ -13037,6 +15353,15 @@
       <c r="F95" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G95" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
@@ -13057,6 +15382,15 @@
       <c r="F96" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G96" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
@@ -13077,6 +15411,15 @@
       <c r="F97" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G97" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
@@ -13097,6 +15440,15 @@
       <c r="F98" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G98" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
@@ -13117,6 +15469,15 @@
       <c r="F99" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G99" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
@@ -13137,6 +15498,15 @@
       <c r="F100" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="G100" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
@@ -13155,6 +15525,15 @@
         <v>3</v>
       </c>
       <c r="F101" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -13173,7 +15552,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.0" customWidth="true"/>
@@ -13182,7 +15561,10 @@
     <col min="4" max="4" width="9.0" customWidth="true"/>
     <col min="5" max="5" width="8.0" customWidth="true"/>
     <col min="6" max="6" width="9.0" customWidth="true"/>
-    <col min="7" max="7" width="11.0" customWidth="true"/>
+    <col min="7" max="7" width="10.0" customWidth="true"/>
+    <col min="8" max="8" width="12.0" customWidth="true"/>
+    <col min="9" max="9" width="11.0" customWidth="true"/>
+    <col min="10" max="10" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -13190,10 +15572,10 @@
         <v>5</v>
       </c>
       <c r="B1" t="s" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s" s="6">
         <v>4</v>
@@ -13204,7 +15586,16 @@
       <c r="F1" t="s" s="6">
         <v>2</v>
       </c>
-      <c r="G1" t="s" s="7">
+      <c r="G1" t="s" s="6">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s" s="6">
         <v>11</v>
       </c>
     </row>
@@ -13230,6 +15621,15 @@
       <c r="G2" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
@@ -13253,6 +15653,15 @@
       <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
@@ -13276,6 +15685,15 @@
       <c r="G4" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
@@ -13299,6 +15717,15 @@
       <c r="G5" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
@@ -13322,6 +15749,15 @@
       <c r="G6" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
@@ -13345,6 +15781,15 @@
       <c r="G7" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
@@ -13368,6 +15813,15 @@
       <c r="G8" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
@@ -13391,6 +15845,15 @@
       <c r="G9" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
@@ -13414,6 +15877,15 @@
       <c r="G10" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
@@ -13437,6 +15909,15 @@
       <c r="G11" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
@@ -13460,6 +15941,15 @@
       <c r="G12" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
@@ -13483,6 +15973,15 @@
       <c r="G13" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
@@ -13506,6 +16005,15 @@
       <c r="G14" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
@@ -13529,6 +16037,15 @@
       <c r="G15" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
@@ -13552,6 +16069,15 @@
       <c r="G16" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
@@ -13575,6 +16101,15 @@
       <c r="G17" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
@@ -13598,6 +16133,15 @@
       <c r="G18" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
@@ -13621,6 +16165,15 @@
       <c r="G19" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
@@ -13644,6 +16197,15 @@
       <c r="G20" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
@@ -13667,6 +16229,15 @@
       <c r="G21" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
@@ -13690,6 +16261,15 @@
       <c r="G22" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H22" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
@@ -13713,6 +16293,15 @@
       <c r="G23" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H23" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
@@ -13736,6 +16325,15 @@
       <c r="G24" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
@@ -13759,6 +16357,15 @@
       <c r="G25" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H25" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
@@ -13782,6 +16389,15 @@
       <c r="G26" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H26" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
@@ -13805,6 +16421,15 @@
       <c r="G27" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
@@ -13828,6 +16453,15 @@
       <c r="G28" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H28" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
@@ -13851,6 +16485,15 @@
       <c r="G29" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H29" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
@@ -13874,6 +16517,15 @@
       <c r="G30" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
@@ -13897,6 +16549,15 @@
       <c r="G31" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H31" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
@@ -13920,6 +16581,15 @@
       <c r="G32" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
@@ -13943,6 +16613,15 @@
       <c r="G33" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H33" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
@@ -13966,6 +16645,15 @@
       <c r="G34" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
@@ -13989,6 +16677,15 @@
       <c r="G35" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
@@ -14012,6 +16709,15 @@
       <c r="G36" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H36" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
@@ -14035,6 +16741,15 @@
       <c r="G37" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H37" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
@@ -14058,6 +16773,15 @@
       <c r="G38" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H38" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
@@ -14081,6 +16805,15 @@
       <c r="G39" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H39" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
@@ -14104,6 +16837,15 @@
       <c r="G40" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H40" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
@@ -14127,6 +16869,15 @@
       <c r="G41" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
@@ -14150,6 +16901,15 @@
       <c r="G42" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
@@ -14173,6 +16933,15 @@
       <c r="G43" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
@@ -14196,6 +16965,15 @@
       <c r="G44" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H44" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
@@ -14219,6 +16997,15 @@
       <c r="G45" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H45" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
@@ -14242,6 +17029,15 @@
       <c r="G46" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
@@ -14265,6 +17061,15 @@
       <c r="G47" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H47" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
@@ -14288,6 +17093,15 @@
       <c r="G48" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H48" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
@@ -14311,6 +17125,15 @@
       <c r="G49" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H49" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
@@ -14334,6 +17157,15 @@
       <c r="G50" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
@@ -14357,6 +17189,15 @@
       <c r="G51" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
@@ -14380,6 +17221,15 @@
       <c r="G52" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
@@ -14403,6 +17253,15 @@
       <c r="G53" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H53" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
@@ -14426,6 +17285,15 @@
       <c r="G54" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H54" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
@@ -14449,6 +17317,15 @@
       <c r="G55" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H55" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
@@ -14472,6 +17349,15 @@
       <c r="G56" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H56" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
@@ -14495,6 +17381,15 @@
       <c r="G57" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H57" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
@@ -14518,6 +17413,15 @@
       <c r="G58" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
@@ -14541,6 +17445,15 @@
       <c r="G59" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H59" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
@@ -14564,6 +17477,15 @@
       <c r="G60" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H60" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
@@ -14587,6 +17509,15 @@
       <c r="G61" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
@@ -14610,6 +17541,15 @@
       <c r="G62" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H62" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
@@ -14633,6 +17573,15 @@
       <c r="G63" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H63" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
@@ -14656,6 +17605,15 @@
       <c r="G64" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H64" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
@@ -14679,6 +17637,15 @@
       <c r="G65" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H65" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
@@ -14702,6 +17669,15 @@
       <c r="G66" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
@@ -14725,6 +17701,15 @@
       <c r="G67" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
@@ -14748,6 +17733,15 @@
       <c r="G68" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H68" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="s">
@@ -14771,6 +17765,15 @@
       <c r="G69" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H69" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="s">
@@ -14794,6 +17797,15 @@
       <c r="G70" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="s">
@@ -14817,6 +17829,15 @@
       <c r="G71" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H71" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="s">
@@ -14840,6 +17861,15 @@
       <c r="G72" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H72" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="s">
@@ -14863,6 +17893,15 @@
       <c r="G73" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H73" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="s">
@@ -14886,6 +17925,15 @@
       <c r="G74" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H74" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="s">
@@ -14909,6 +17957,15 @@
       <c r="G75" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H75" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="s">
@@ -14932,6 +17989,15 @@
       <c r="G76" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H76" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="s">
@@ -14955,6 +18021,15 @@
       <c r="G77" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="s">
@@ -14978,6 +18053,15 @@
       <c r="G78" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H78" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="s">
@@ -15001,6 +18085,15 @@
       <c r="G79" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H79" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="s">
@@ -15024,6 +18117,15 @@
       <c r="G80" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H80" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="s">
@@ -15047,6 +18149,15 @@
       <c r="G81" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H81" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="s">
@@ -15070,6 +18181,15 @@
       <c r="G82" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H82" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="s">
@@ -15093,6 +18213,15 @@
       <c r="G83" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H83" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="s">
@@ -15116,6 +18245,15 @@
       <c r="G84" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H84" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="s">
@@ -15139,6 +18277,15 @@
       <c r="G85" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H85" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="s">
@@ -15162,6 +18309,15 @@
       <c r="G86" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H86" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="s">
@@ -15185,6 +18341,15 @@
       <c r="G87" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H87" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="s">
@@ -15208,6 +18373,15 @@
       <c r="G88" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H88" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="s">
@@ -15231,6 +18405,15 @@
       <c r="G89" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H89" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="s">
@@ -15254,6 +18437,15 @@
       <c r="G90" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H90" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="s">
@@ -15277,6 +18469,15 @@
       <c r="G91" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H91" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="s">
@@ -15300,6 +18501,15 @@
       <c r="G92" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H92" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="s">
@@ -15323,6 +18533,15 @@
       <c r="G93" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H93" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="s">
@@ -15346,6 +18565,15 @@
       <c r="G94" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H94" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="s">
@@ -15369,6 +18597,15 @@
       <c r="G95" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H95" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="s">
@@ -15392,6 +18629,15 @@
       <c r="G96" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H96" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="s">
@@ -15415,6 +18661,15 @@
       <c r="G97" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H97" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="s">
@@ -15438,6 +18693,15 @@
       <c r="G98" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H98" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="s">
@@ -15461,6 +18725,15 @@
       <c r="G99" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H99" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="s">
@@ -15484,6 +18757,15 @@
       <c r="G100" s="8" t="s">
         <v>3</v>
       </c>
+      <c r="H100" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="s">
@@ -15505,6 +18787,15 @@
         <v>3</v>
       </c>
       <c r="G101" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -15532,10 +18823,10 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s" s="10">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
@@ -16345,7 +19636,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.0" customWidth="true"/>
@@ -16369,95 +19660,99 @@
     <col min="19" max="19" width="13.0" customWidth="true"/>
     <col min="20" max="20" width="12.0" customWidth="true"/>
     <col min="21" max="21" width="10.0" customWidth="true"/>
-    <col min="22" max="22" width="12.0" customWidth="true"/>
+    <col min="22" max="22" width="10.0" customWidth="true"/>
     <col min="23" max="23" width="9.0" customWidth="true"/>
-    <col min="24" max="24" width="10.0" customWidth="true"/>
+    <col min="24" max="24" width="8.0" customWidth="true"/>
     <col min="25" max="25" width="9.0" customWidth="true"/>
-    <col min="26" max="26" width="8.0" customWidth="true"/>
-    <col min="27" max="27" width="9.0" customWidth="true"/>
+    <col min="26" max="26" width="10.0" customWidth="true"/>
+    <col min="27" max="27" width="12.0" customWidth="true"/>
+    <col min="28" max="28" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s" s="12">
         <v>5</v>
       </c>
       <c r="C1" t="s" s="12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s" s="12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s" s="12">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s" s="12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s" s="12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s" s="12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s" s="12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s" s="12">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s" s="12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s" s="12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M1" t="s" s="12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N1" t="s" s="12">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O1" t="s" s="12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P1" t="s" s="12">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q1" t="s" s="12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R1" t="s" s="12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S1" t="s" s="12">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T1" t="s" s="12">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="U1" t="s" s="12">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="V1" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="W1" t="s" s="13">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="W1" t="s" s="12">
+        <v>4</v>
       </c>
       <c r="X1" t="s" s="12">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="Y1" t="s" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z1" t="s" s="12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA1" t="s" s="12">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="AB1" t="s" s="12">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -16542,6 +19837,9 @@
       <c r="AA2" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB2" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="s">
@@ -16625,6 +19923,9 @@
       <c r="AA3" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB3" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="s">
@@ -16708,6 +20009,9 @@
       <c r="AA4" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB4" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
@@ -16791,6 +20095,9 @@
       <c r="AA5" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB5" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
@@ -16874,6 +20181,9 @@
       <c r="AA6" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB6" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
@@ -16957,6 +20267,9 @@
       <c r="AA7" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB7" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
@@ -17040,6 +20353,9 @@
       <c r="AA8" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB8" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
@@ -17123,6 +20439,9 @@
       <c r="AA9" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB9" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
@@ -17206,6 +20525,9 @@
       <c r="AA10" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB10" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
@@ -17289,6 +20611,9 @@
       <c r="AA11" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB11" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
@@ -17372,6 +20697,9 @@
       <c r="AA12" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB12" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
@@ -17455,6 +20783,9 @@
       <c r="AA13" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB13" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="s">
@@ -17538,6 +20869,9 @@
       <c r="AA14" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB14" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="s">
@@ -17621,6 +20955,9 @@
       <c r="AA15" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB15" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="s">
@@ -17704,6 +21041,9 @@
       <c r="AA16" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB16" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="s">
@@ -17787,6 +21127,9 @@
       <c r="AA17" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB17" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
@@ -17870,6 +21213,9 @@
       <c r="AA18" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB18" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="s">
@@ -17953,6 +21299,9 @@
       <c r="AA19" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB19" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="s">
@@ -18036,6 +21385,9 @@
       <c r="AA20" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB20" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="s">
@@ -18119,6 +21471,9 @@
       <c r="AA21" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB21" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="s">
@@ -18202,6 +21557,9 @@
       <c r="AA22" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB22" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="s">
@@ -18285,6 +21643,9 @@
       <c r="AA23" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB23" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="s">
@@ -18368,6 +21729,9 @@
       <c r="AA24" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB24" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
@@ -18451,6 +21815,9 @@
       <c r="AA25" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB25" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
@@ -18534,6 +21901,9 @@
       <c r="AA26" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB26" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
@@ -18617,6 +21987,9 @@
       <c r="AA27" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB27" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
@@ -18700,6 +22073,9 @@
       <c r="AA28" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB28" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="s">
@@ -18783,6 +22159,9 @@
       <c r="AA29" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB29" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="s">
@@ -18866,6 +22245,9 @@
       <c r="AA30" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB30" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="s">
@@ -18949,6 +22331,9 @@
       <c r="AA31" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB31" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="s">
@@ -19032,6 +22417,9 @@
       <c r="AA32" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB32" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="s">
@@ -19115,6 +22503,9 @@
       <c r="AA33" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB33" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="s">
@@ -19198,6 +22589,9 @@
       <c r="AA34" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB34" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="s">
@@ -19281,6 +22675,9 @@
       <c r="AA35" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB35" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="s">
@@ -19364,6 +22761,9 @@
       <c r="AA36" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB36" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="s">
@@ -19447,6 +22847,9 @@
       <c r="AA37" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB37" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="s">
@@ -19530,6 +22933,9 @@
       <c r="AA38" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB38" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="s">
@@ -19613,6 +23019,9 @@
       <c r="AA39" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB39" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="s">
@@ -19696,6 +23105,9 @@
       <c r="AA40" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB40" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="s">
@@ -19779,6 +23191,9 @@
       <c r="AA41" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB41" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="s">
@@ -19862,6 +23277,9 @@
       <c r="AA42" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB42" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="s">
@@ -19945,6 +23363,9 @@
       <c r="AA43" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB43" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="s">
@@ -20028,6 +23449,9 @@
       <c r="AA44" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB44" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="s">
@@ -20111,6 +23535,9 @@
       <c r="AA45" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB45" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="s">
@@ -20194,6 +23621,9 @@
       <c r="AA46" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB46" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="s">
@@ -20277,6 +23707,9 @@
       <c r="AA47" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB47" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="s">
@@ -20360,6 +23793,9 @@
       <c r="AA48" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB48" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="s">
@@ -20443,6 +23879,9 @@
       <c r="AA49" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB49" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="s">
@@ -20526,6 +23965,9 @@
       <c r="AA50" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB50" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="s">
@@ -20609,6 +24051,9 @@
       <c r="AA51" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB51" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="s">
@@ -20692,6 +24137,9 @@
       <c r="AA52" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB52" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="s">
@@ -20775,6 +24223,9 @@
       <c r="AA53" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB53" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="s">
@@ -20858,6 +24309,9 @@
       <c r="AA54" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB54" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="s">
@@ -20941,6 +24395,9 @@
       <c r="AA55" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB55" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="s">
@@ -21024,6 +24481,9 @@
       <c r="AA56" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB56" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="s">
@@ -21107,6 +24567,9 @@
       <c r="AA57" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB57" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="s">
@@ -21190,6 +24653,9 @@
       <c r="AA58" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB58" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="s">
@@ -21273,6 +24739,9 @@
       <c r="AA59" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB59" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="s">
@@ -21356,6 +24825,9 @@
       <c r="AA60" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB60" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="s">
@@ -21439,6 +24911,9 @@
       <c r="AA61" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB61" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="s">
@@ -21522,6 +24997,9 @@
       <c r="AA62" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB62" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="s">
@@ -21605,6 +25083,9 @@
       <c r="AA63" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB63" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="s">
@@ -21688,6 +25169,9 @@
       <c r="AA64" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB64" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="s">
@@ -21771,6 +25255,9 @@
       <c r="AA65" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB65" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="s">
@@ -21854,6 +25341,9 @@
       <c r="AA66" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB66" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="s">
@@ -21937,6 +25427,9 @@
       <c r="AA67" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB67" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="s">
@@ -22020,6 +25513,9 @@
       <c r="AA68" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB68" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="s">
@@ -22103,6 +25599,9 @@
       <c r="AA69" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB69" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="s">
@@ -22186,6 +25685,9 @@
       <c r="AA70" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB70" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="s">
@@ -22269,6 +25771,9 @@
       <c r="AA71" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB71" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="s">
@@ -22352,6 +25857,9 @@
       <c r="AA72" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB72" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="s">
@@ -22435,6 +25943,9 @@
       <c r="AA73" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB73" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="s">
@@ -22518,6 +26029,9 @@
       <c r="AA74" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB74" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="s">
@@ -22601,6 +26115,9 @@
       <c r="AA75" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB75" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="s">
@@ -22684,6 +26201,9 @@
       <c r="AA76" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB76" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="s">
@@ -22767,6 +26287,9 @@
       <c r="AA77" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB77" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="s">
@@ -22850,6 +26373,9 @@
       <c r="AA78" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB78" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="s">
@@ -22933,6 +26459,9 @@
       <c r="AA79" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB79" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="s">
@@ -23016,6 +26545,9 @@
       <c r="AA80" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB80" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="s">
@@ -23099,6 +26631,9 @@
       <c r="AA81" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB81" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="s">
@@ -23182,6 +26717,9 @@
       <c r="AA82" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB82" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="s">
@@ -23265,6 +26803,9 @@
       <c r="AA83" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB83" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="s">
@@ -23348,6 +26889,9 @@
       <c r="AA84" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB84" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="s">
@@ -23431,6 +26975,9 @@
       <c r="AA85" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB85" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="s">
@@ -23514,6 +27061,9 @@
       <c r="AA86" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB86" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="s">
@@ -23597,6 +27147,9 @@
       <c r="AA87" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB87" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="s">
@@ -23680,6 +27233,9 @@
       <c r="AA88" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB88" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="s">
@@ -23763,6 +27319,9 @@
       <c r="AA89" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB89" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="s">
@@ -23846,6 +27405,9 @@
       <c r="AA90" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB90" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="s">
@@ -23929,6 +27491,9 @@
       <c r="AA91" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB91" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="s">
@@ -24012,6 +27577,9 @@
       <c r="AA92" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB92" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="s">
@@ -24095,6 +27663,9 @@
       <c r="AA93" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB93" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="s">
@@ -24178,6 +27749,9 @@
       <c r="AA94" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB94" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="s">
@@ -24261,6 +27835,9 @@
       <c r="AA95" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB95" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="s">
@@ -24344,6 +27921,9 @@
       <c r="AA96" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB96" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="s">
@@ -24427,6 +28007,9 @@
       <c r="AA97" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB97" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="s">
@@ -24510,6 +28093,9 @@
       <c r="AA98" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB98" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="s">
@@ -24593,6 +28179,9 @@
       <c r="AA99" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB99" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="s">
@@ -24676,6 +28265,9 @@
       <c r="AA100" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="AB100" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="s">
@@ -24757,6 +28349,9 @@
         <v>3</v>
       </c>
       <c r="AA101" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="14" t="s">
         <v>3</v>
       </c>
     </row>
@@ -24792,7 +28387,7 @@
     <dataValidation type="list" sqref="T2:T101" allowBlank="true" errorStyle="stop">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AA2:AA101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="Y2:Y101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24814,19 +28409,19 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="16">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="16">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -26548,19 +30143,19 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="19">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="19">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s" s="18">
         <v>41</v>
       </c>
-      <c r="D1" t="s" s="18">
-        <v>40</v>
-      </c>
       <c r="E1" t="s" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -28270,7 +31865,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.0" customWidth="true"/>
@@ -28279,7 +31874,10 @@
     <col min="4" max="4" width="9.0" customWidth="true"/>
     <col min="5" max="5" width="8.0" customWidth="true"/>
     <col min="6" max="6" width="9.0" customWidth="true"/>
-    <col min="7" max="7" width="11.0" customWidth="true"/>
+    <col min="7" max="7" width="10.0" customWidth="true"/>
+    <col min="8" max="8" width="12.0" customWidth="true"/>
+    <col min="9" max="9" width="11.0" customWidth="true"/>
+    <col min="10" max="10" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -28287,10 +31885,10 @@
         <v>5</v>
       </c>
       <c r="B1" t="s" s="21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s" s="21">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s" s="21">
         <v>4</v>
@@ -28301,7 +31899,16 @@
       <c r="F1" t="s" s="21">
         <v>2</v>
       </c>
-      <c r="G1" t="s" s="22">
+      <c r="G1" t="s" s="21">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s" s="21">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s" s="22">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s" s="21">
         <v>11</v>
       </c>
     </row>
@@ -28327,6 +31934,15 @@
       <c r="G2" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="23" t="s">
@@ -28350,6 +31966,15 @@
       <c r="G3" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H3" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="s">
@@ -28373,6 +31998,15 @@
       <c r="G4" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="23" t="s">
@@ -28396,6 +32030,15 @@
       <c r="G5" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H5" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="s">
@@ -28419,6 +32062,15 @@
       <c r="G6" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="s">
@@ -28442,6 +32094,15 @@
       <c r="G7" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H7" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="s">
@@ -28465,6 +32126,15 @@
       <c r="G8" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H8" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="s">
@@ -28488,6 +32158,15 @@
       <c r="G9" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="s">
@@ -28511,6 +32190,15 @@
       <c r="G10" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H10" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="s">
@@ -28534,6 +32222,15 @@
       <c r="G11" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H11" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="s">
@@ -28557,6 +32254,15 @@
       <c r="G12" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H12" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
@@ -28580,6 +32286,15 @@
       <c r="G13" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
@@ -28603,6 +32318,15 @@
       <c r="G14" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H14" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
@@ -28626,6 +32350,15 @@
       <c r="G15" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H15" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="s">
@@ -28649,6 +32382,15 @@
       <c r="G16" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H16" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="s">
@@ -28672,6 +32414,15 @@
       <c r="G17" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H17" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="s">
@@ -28695,6 +32446,15 @@
       <c r="G18" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H18" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="s">
@@ -28718,6 +32478,15 @@
       <c r="G19" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H19" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="s">
@@ -28741,6 +32510,15 @@
       <c r="G20" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H20" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="s">
@@ -28764,6 +32542,15 @@
       <c r="G21" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H21" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="s">
@@ -28787,6 +32574,15 @@
       <c r="G22" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H22" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="s">
@@ -28810,6 +32606,15 @@
       <c r="G23" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H23" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="s">
@@ -28833,6 +32638,15 @@
       <c r="G24" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H24" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="s">
@@ -28856,6 +32670,15 @@
       <c r="G25" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H25" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="s">
@@ -28879,6 +32702,15 @@
       <c r="G26" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H26" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="s">
@@ -28902,6 +32734,15 @@
       <c r="G27" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H27" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="s">
@@ -28925,6 +32766,15 @@
       <c r="G28" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H28" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="s">
@@ -28948,6 +32798,15 @@
       <c r="G29" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H29" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="s">
@@ -28971,6 +32830,15 @@
       <c r="G30" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H30" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J30" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="s">
@@ -28994,6 +32862,15 @@
       <c r="G31" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H31" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="s">
@@ -29017,6 +32894,15 @@
       <c r="G32" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H32" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="s">
@@ -29040,6 +32926,15 @@
       <c r="G33" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H33" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="s">
@@ -29063,6 +32958,15 @@
       <c r="G34" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H34" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="s">
@@ -29086,6 +32990,15 @@
       <c r="G35" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H35" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="s">
@@ -29109,6 +33022,15 @@
       <c r="G36" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H36" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="s">
@@ -29132,6 +33054,15 @@
       <c r="G37" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H37" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J37" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="s">
@@ -29155,6 +33086,15 @@
       <c r="G38" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H38" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="s">
@@ -29178,6 +33118,15 @@
       <c r="G39" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H39" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="s">
@@ -29201,6 +33150,15 @@
       <c r="G40" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H40" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="s">
@@ -29224,6 +33182,15 @@
       <c r="G41" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H41" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="s">
@@ -29247,6 +33214,15 @@
       <c r="G42" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H42" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="s">
@@ -29270,6 +33246,15 @@
       <c r="G43" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H43" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="s">
@@ -29293,6 +33278,15 @@
       <c r="G44" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H44" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="s">
@@ -29316,6 +33310,15 @@
       <c r="G45" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H45" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="s">
@@ -29339,6 +33342,15 @@
       <c r="G46" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H46" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="23" t="s">
@@ -29362,6 +33374,15 @@
       <c r="G47" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H47" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="s">
@@ -29385,6 +33406,15 @@
       <c r="G48" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H48" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="s">
@@ -29408,6 +33438,15 @@
       <c r="G49" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H49" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="s">
@@ -29431,6 +33470,15 @@
       <c r="G50" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H50" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="s">
@@ -29454,6 +33502,15 @@
       <c r="G51" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H51" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="23" t="s">
@@ -29477,6 +33534,15 @@
       <c r="G52" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H52" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="s">
@@ -29500,6 +33566,15 @@
       <c r="G53" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H53" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J53" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="23" t="s">
@@ -29523,6 +33598,15 @@
       <c r="G54" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H54" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="23" t="s">
@@ -29546,6 +33630,15 @@
       <c r="G55" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H55" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="s">
@@ -29569,6 +33662,15 @@
       <c r="G56" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H56" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="23" t="s">
@@ -29592,6 +33694,15 @@
       <c r="G57" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H57" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="23" t="s">
@@ -29615,6 +33726,15 @@
       <c r="G58" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H58" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="s">
@@ -29638,6 +33758,15 @@
       <c r="G59" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H59" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="23" t="s">
@@ -29661,6 +33790,15 @@
       <c r="G60" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H60" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="23" t="s">
@@ -29684,6 +33822,15 @@
       <c r="G61" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H61" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J61" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="s">
@@ -29707,6 +33854,15 @@
       <c r="G62" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H62" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="s">
@@ -29730,6 +33886,15 @@
       <c r="G63" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H63" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I63" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J63" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="23" t="s">
@@ -29753,6 +33918,15 @@
       <c r="G64" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H64" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J64" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="s">
@@ -29776,6 +33950,15 @@
       <c r="G65" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H65" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I65" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J65" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="23" t="s">
@@ -29799,6 +33982,15 @@
       <c r="G66" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H66" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="23" t="s">
@@ -29822,6 +34014,15 @@
       <c r="G67" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H67" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J67" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="23" t="s">
@@ -29845,6 +34046,15 @@
       <c r="G68" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H68" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I68" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J68" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="s">
@@ -29868,6 +34078,15 @@
       <c r="G69" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H69" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I69" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J69" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="23" t="s">
@@ -29891,6 +34110,15 @@
       <c r="G70" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H70" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I70" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J70" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="s">
@@ -29914,6 +34142,15 @@
       <c r="G71" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H71" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J71" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="23" t="s">
@@ -29937,6 +34174,15 @@
       <c r="G72" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H72" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="s">
@@ -29960,6 +34206,15 @@
       <c r="G73" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H73" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I73" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J73" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="23" t="s">
@@ -29983,6 +34238,15 @@
       <c r="G74" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H74" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I74" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J74" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="23" t="s">
@@ -30006,6 +34270,15 @@
       <c r="G75" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H75" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J75" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="23" t="s">
@@ -30029,6 +34302,15 @@
       <c r="G76" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H76" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="23" t="s">
@@ -30052,6 +34334,15 @@
       <c r="G77" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H77" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J77" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="23" t="s">
@@ -30075,6 +34366,15 @@
       <c r="G78" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H78" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J78" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="s">
@@ -30098,6 +34398,15 @@
       <c r="G79" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H79" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I79" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J79" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="23" t="s">
@@ -30121,6 +34430,15 @@
       <c r="G80" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H80" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="23" t="s">
@@ -30144,6 +34462,15 @@
       <c r="G81" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H81" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="23" t="s">
@@ -30167,6 +34494,15 @@
       <c r="G82" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H82" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J82" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="23" t="s">
@@ -30190,6 +34526,15 @@
       <c r="G83" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H83" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="23" t="s">
@@ -30213,6 +34558,15 @@
       <c r="G84" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H84" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I84" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J84" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="23" t="s">
@@ -30236,6 +34590,15 @@
       <c r="G85" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H85" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I85" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J85" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="23" t="s">
@@ -30259,6 +34622,15 @@
       <c r="G86" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H86" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J86" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="23" t="s">
@@ -30282,6 +34654,15 @@
       <c r="G87" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H87" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I87" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J87" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="23" t="s">
@@ -30305,6 +34686,15 @@
       <c r="G88" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H88" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I88" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J88" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="23" t="s">
@@ -30328,6 +34718,15 @@
       <c r="G89" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H89" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="s">
@@ -30351,6 +34750,15 @@
       <c r="G90" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H90" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I90" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J90" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="s">
@@ -30374,6 +34782,15 @@
       <c r="G91" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H91" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="s">
@@ -30397,6 +34814,15 @@
       <c r="G92" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H92" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I92" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J92" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="23" t="s">
@@ -30420,6 +34846,15 @@
       <c r="G93" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H93" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I93" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J93" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="23" t="s">
@@ -30443,6 +34878,15 @@
       <c r="G94" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H94" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="s">
@@ -30466,6 +34910,15 @@
       <c r="G95" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H95" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I95" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J95" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="23" t="s">
@@ -30489,6 +34942,15 @@
       <c r="G96" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H96" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="23" t="s">
@@ -30512,6 +34974,15 @@
       <c r="G97" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H97" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I97" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J97" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="23" t="s">
@@ -30535,6 +35006,15 @@
       <c r="G98" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H98" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I98" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J98" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="23" t="s">
@@ -30558,6 +35038,15 @@
       <c r="G99" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H99" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I99" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J99" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="23" t="s">
@@ -30581,6 +35070,15 @@
       <c r="G100" s="23" t="s">
         <v>3</v>
       </c>
+      <c r="H100" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="23" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="23" t="s">
@@ -30602,6 +35100,15 @@
         <v>3</v>
       </c>
       <c r="G101" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="23" t="s">
         <v>3</v>
       </c>
     </row>
@@ -30632,10 +35139,10 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="25">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s" s="25">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
